--- a/artfynd/A 34322-2021 artfynd.xlsx
+++ b/artfynd/A 34322-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131236290</v>
       </c>
       <c r="B2" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131236167</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131235752</v>
+        <v>131236495</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504836</v>
+        <v>504860</v>
       </c>
       <c r="R4" t="n">
-        <v>6699938</v>
+        <v>6700261</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131236495</v>
+        <v>131235752</v>
       </c>
       <c r="B5" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504860</v>
+        <v>504836</v>
       </c>
       <c r="R5" t="n">
-        <v>6700261</v>
+        <v>6699938</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>131236489</v>
       </c>
       <c r="B6" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34322-2021 artfynd.xlsx
+++ b/artfynd/A 34322-2021 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131236495</v>
+        <v>131235752</v>
       </c>
       <c r="B4" t="n">
         <v>79260</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504860</v>
+        <v>504836</v>
       </c>
       <c r="R4" t="n">
-        <v>6700261</v>
+        <v>6699938</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131235752</v>
+        <v>131236495</v>
       </c>
       <c r="B5" t="n">
         <v>79260</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504836</v>
+        <v>504860</v>
       </c>
       <c r="R5" t="n">
-        <v>6699938</v>
+        <v>6700261</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34322-2021 artfynd.xlsx
+++ b/artfynd/A 34322-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131236290</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131236167</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131235752</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131236495</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>131236489</v>
       </c>
       <c r="B6" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34322-2021 artfynd.xlsx
+++ b/artfynd/A 34322-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131236290</v>
       </c>
       <c r="B2" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131236167</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131235752</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131236495</v>
       </c>
       <c r="B5" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>131236489</v>
       </c>
       <c r="B6" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34322-2021 artfynd.xlsx
+++ b/artfynd/A 34322-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131236290</v>
+        <v>131235752</v>
       </c>
       <c r="B2" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504866</v>
+        <v>504836</v>
       </c>
       <c r="R2" t="n">
-        <v>6699879</v>
+        <v>6699938</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,11 +785,11 @@
         <v>131236167</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -889,14 +889,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131235752</v>
+        <v>131236290</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504836</v>
+        <v>504866</v>
       </c>
       <c r="R4" t="n">
-        <v>6699938</v>
+        <v>6699879</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,11 +999,11 @@
         <v>131236495</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1100,109 +1100,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>131236489</v>
-      </c>
-      <c r="B6" t="n">
-        <v>91852</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Tryssjön, Dlr</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>504866</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6699879</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Gagnef</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Gagnef</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Tobias Hellberg</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Tobias Hellberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
